--- a/TimeStamped_Participants/tex_shun_directional.xlsx
+++ b/TimeStamped_Participants/tex_shun_directional.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imlit\Downloads\Formatted Participants\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REEF\SIT\Fall2024\Github\MyBeat_avg_graph\MyBeat\TimeStamped_Participants\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38578711-37B2-41C2-BEEC-D71E05F430E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD3A0D4-00CA-4A95-A614-B689B608299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{37CF937B-F156-43DD-99DC-B5FD29A0E783}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -573,6 +574,6725 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Directional Model</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LF/HF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$899</c:f>
+              <c:numCache>
+                <c:formatCode>h:mm:ss</c:formatCode>
+                <c:ptCount val="898"/>
+                <c:pt idx="0">
+                  <c:v>0.67708333333333337</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67709490740740741</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67709490740740741</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67710648148148145</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6771180555555556</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6771180555555556</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.67712962962962964</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.67714120370370368</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.67714120370370368</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67715277777777783</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.67716435185185186</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.67716435185185186</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.6771759259259259</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.6771759259259259</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67718750000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.67719907407407409</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.67719907407407409</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.67721064814814813</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.67722222222222217</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67722222222222217</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.67723379629629632</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.67724537037037036</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.67724537037037036</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.6772569444444444</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.67726851851851855</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.67726851851851855</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.67728009259259259</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.67729166666666663</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.67729166666666663</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.67730324074074078</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.67730324074074078</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.67731481481481481</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.67732638888888885</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.67732638888888885</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.677337962962963</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.67734953703703704</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.67734953703703704</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.67736111111111108</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.67737268518518523</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.67737268518518523</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.67738425925925927</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.67739583333333331</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.67739583333333331</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.67740740740740746</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.6774189814814815</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.6774189814814815</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.67743055555555554</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.67743055555555554</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.67744212962962957</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.67745370370370372</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.67745370370370372</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.67746527777777776</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.6774768518518518</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.6774768518518518</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.67748842592592595</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.67749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.67749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.67751157407407403</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.67752314814814818</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.67752314814814818</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.67753472222222222</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.67754629629629626</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.67754629629629626</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.67755787037037041</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.67756944444444445</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.67756944444444445</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.67758101851851849</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.67758101851851849</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.67759259259259264</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.67760416666666667</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.67760416666666667</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.67761574074074071</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.67762731481481486</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.67762731481481486</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.6776388888888889</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.67765046296296294</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.67765046296296294</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.67766203703703709</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.67767361111111113</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.67767361111111113</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.67768518518518517</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.67769675925925921</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.67769675925925921</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.67770833333333336</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.6777199074074074</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.6777199074074074</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.67773148148148143</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.67774305555555558</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.67774305555555558</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.67775462962962962</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.67775462962962962</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.67776620370370366</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.67777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.67777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.67778935185185185</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.67780092592592589</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.67780092592592589</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.67781250000000004</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.67782407407407408</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.67782407407407408</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.67783564814814812</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.67784722222222227</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.67784722222222227</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.67785879629629631</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.67787037037037035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.67787037037037035</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.6778819444444445</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.67789351851851853</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.67789351851851853</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.67790509259259257</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.67791666666666661</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.67791666666666661</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.67792824074074076</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.6779398148148148</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.67795138888888884</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.67795138888888884</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.67796296296296299</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.67797453703703703</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.67797453703703703</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.67798611111111107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.67799768518518522</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.67799768518518522</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.67800925925925926</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.67802083333333329</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.67802083333333329</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.67803240740740744</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.67804398148148148</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.67804398148148148</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.67805555555555552</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.67806712962962967</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.67806712962962967</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.67807870370370371</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.67809027777777775</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.6781018518518519</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.6781018518518519</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.67811342592592594</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.67811342592592594</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.67812499999999998</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.67813657407407413</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.67813657407407413</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.67814814814814817</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.67815972222222221</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.67817129629629624</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.67817129629629624</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.67818287037037039</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.67818287037037039</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.67819444444444443</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.67820601851851847</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.67820601851851847</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.67821759259259262</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.67822916666666666</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.67822916666666666</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.6782407407407407</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.67825231481481485</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.67825231481481485</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.67826388888888889</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.67827546296296293</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.67827546296296293</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.67828703703703708</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.67829861111111112</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.67829861111111112</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.67831018518518515</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.6783217592592593</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.6783217592592593</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.67833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.67834490740740738</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.67834490740740738</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.67835648148148153</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.67836805555555557</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.67836805555555557</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.67837962962962961</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.67839120370370365</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.67839120370370365</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.6784027777777778</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.67841435185185184</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.67841435185185184</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.67842592592592588</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.67843750000000003</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.67843750000000003</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.67844907407407407</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.6784606481481481</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.6784606481481481</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.67847222222222225</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.67848379629629629</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.67848379629629629</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.67849537037037033</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.67850694444444448</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.67850694444444448</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.67851851851851852</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.67853009259259256</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.67853009259259256</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.67854166666666671</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.67855324074074075</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.67855324074074075</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.67856481481481479</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.67857638888888894</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.67857638888888894</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.67858796296296298</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.67859953703703701</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.67859953703703701</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.67861111111111116</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.6786226851851852</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.6786226851851852</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.67863425925925924</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.67864583333333328</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.67864583333333328</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.67865740740740743</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.67865740740740743</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.67866898148148147</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.67868055555555551</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.67868055555555551</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.67869212962962966</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.6787037037037037</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.6787037037037037</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.67871527777777774</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.67872685185185189</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.67872685185185189</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.67873842592592593</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.67874999999999996</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.67874999999999996</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.67876157407407411</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.67877314814814815</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.67877314814814815</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.67878472222222219</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.67879629629629634</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.67879629629629634</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.67880787037037038</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.67881944444444442</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.67881944444444442</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.67883101851851857</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.67884259259259261</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.67884259259259261</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.67885416666666665</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.67886574074074069</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.67886574074074069</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.67887731481481484</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.67888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.67888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.67890046296296291</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.67891203703703706</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.67891203703703706</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.6789236111111111</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.67893518518518514</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.67893518518518514</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.67894675925925929</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.67894675925925929</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.67895833333333333</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.67896990740740737</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.67896990740740737</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.67898148148148152</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.67899305555555556</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.67899305555555556</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.6790046296296296</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.67901620370370375</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.67901620370370375</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.67902777777777779</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.67903935185185182</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.67903935185185182</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.67905092592592597</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.67906250000000001</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.67906250000000001</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.67907407407407405</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.6790856481481482</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.6790856481481482</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.67909722222222224</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.67909722222222224</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.67910879629629628</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.67912037037037032</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.67912037037037032</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.67913194444444447</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.67914351851851851</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.67914351851851851</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.67915509259259255</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.6791666666666667</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.6791666666666667</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.67917824074074074</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.67917824074074074</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.67918981481481477</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.67920138888888892</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.67921296296296296</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.67921296296296296</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.679224537037037</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.67923611111111115</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.67923611111111115</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.67924768518518519</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.67925925925925923</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.67925925925925923</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.67927083333333338</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.67928240740740742</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.67928240740740742</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.67929398148148146</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.67929398148148146</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.67930555555555561</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.67931712962962965</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.67931712962962965</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.67932870370370368</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.67934027777777772</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.67935185185185187</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.67935185185185187</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.67936342592592591</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.67937499999999995</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.67937499999999995</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.6793865740740741</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.67939814814814814</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.67939814814814814</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.67940972222222218</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.67942129629629633</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.67943287037037037</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.67943287037037037</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.67944444444444441</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.67945601851851856</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.67945601851851856</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.6794675925925926</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.67947916666666663</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.67947916666666663</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.67949074074074078</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.67950231481481482</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.67950231481481482</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.67951388888888886</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.67952546296296301</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.67952546296296301</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.67953703703703705</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.67954861111111109</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.67954861111111109</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.67956018518518524</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.67957175925925928</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.67957175925925928</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.67958333333333332</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.67959490740740736</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.67959490740740736</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.67960648148148151</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.67961805555555554</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.67961805555555554</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.67962962962962958</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.67964120370370373</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.67964120370370373</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.67965277777777777</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.67966435185185181</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.67966435185185181</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.67967592592592596</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.6796875</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.6796875</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.67969907407407404</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.67969907407407404</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.67971064814814819</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.67972222222222223</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.67972222222222223</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.67973379629629627</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.67974537037037042</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.67974537037037042</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.67975694444444446</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.67976851851851849</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.67976851851851849</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.67978009259259264</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.67979166666666668</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.67979166666666668</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.67980324074074072</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.67981481481481476</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.67981481481481476</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.67982638888888891</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.67983796296296295</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.67983796296296295</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.67984953703703699</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.67986111111111114</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.67986111111111114</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.67987268518518518</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.67988425925925922</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.67988425925925922</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.67989583333333337</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.6799074074074074</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.6799074074074074</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.67991898148148144</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.67993055555555559</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.67993055555555559</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.67994212962962963</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.67995370370370367</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.67995370370370367</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.67996527777777782</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.67996527777777782</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.67997685185185186</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.6799884259259259</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.6799884259259259</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.68001157407407409</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.68001157407407409</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.68002314814814813</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.68003472222222228</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.68003472222222228</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.68004629629629632</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.68005787037037035</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.68005787037037035</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.68006944444444439</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.68006944444444439</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.68008101851851854</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.68009259259259258</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.68009259259259258</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.68010416666666662</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.68011574074074077</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.68012731481481481</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.68012731481481481</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.68013888888888885</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.680150462962963</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.680150462962963</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.68016203703703704</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.68017361111111108</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.68017361111111108</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.68018518518518523</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.68019675925925926</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.68019675925925926</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.6802083333333333</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.68021990740740745</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.68021990740740745</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.68023148148148149</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.68024305555555553</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.68025462962962968</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.68025462962962968</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.68026620370370372</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.68027777777777776</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.6802893518518518</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.6802893518518518</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.68030092592592595</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.68031249999999999</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.68031249999999999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.68032407407407403</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.68033564814814818</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.68033564814814818</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.68034722222222221</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.68035879629629625</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.68035879629629625</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.6803703703703704</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.68038194444444444</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.68039351851851848</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.68039351851851848</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.68040509259259263</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.68041666666666667</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.68041666666666667</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.68042824074074071</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.68043981481481486</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.68043981481481486</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.6804513888888889</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.68046296296296294</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.68046296296296294</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.68047453703703709</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.68048611111111112</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.68048611111111112</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.68049768518518516</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.68050925925925931</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.68050925925925931</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.68052083333333335</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.68053240740740739</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.68053240740740739</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.68054398148148143</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.68055555555555558</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.68055555555555558</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.68056712962962962</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.68057870370370366</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.68057870370370366</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.68059027777777781</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.68060185185185185</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.68060185185185185</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.68061342592592589</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.68062500000000004</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.68062500000000004</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.68063657407407407</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.68064814814814811</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.68064814814814811</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.68065972222222226</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.68065972222222226</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.6806712962962963</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.68068287037037034</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.68068287037037034</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.68069444444444449</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.68070601851851853</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.68070601851851853</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.68071759259259257</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.68072916666666672</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.68072916666666672</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.68074074074074076</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.6807523148148148</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.6807523148148148</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.68076388888888884</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.68077546296296299</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.68077546296296299</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.68078703703703702</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.68079861111111106</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.68079861111111106</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.68081018518518521</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.68082175925925925</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.68082175925925925</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.68083333333333329</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.68084490740740744</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.68085648148148148</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.68085648148148148</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.68086805555555552</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.68087962962962967</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.68087962962962967</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.68089120370370371</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.68090277777777775</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.68090277777777775</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.6809143518518519</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>0.68092592592592593</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>0.68092592592592593</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0.68093749999999997</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>0.68094907407407412</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>0.68096064814814816</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>0.68096064814814816</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>0.6809722222222222</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>0.68098379629629635</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>0.68098379629629635</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>0.68099537037037039</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>0.68100694444444443</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>0.68101851851851847</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>0.68101851851851847</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>0.68103009259259262</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>0.68104166666666666</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>0.68104166666666666</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>0.6810532407407407</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>0.68106481481481485</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>0.68106481481481485</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>0.68107638888888888</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>0.68108796296296292</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>0.68108796296296292</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>0.68109953703703707</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>0.68111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>0.68111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>0.68112268518518515</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>0.6811342592592593</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>0.6811342592592593</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>0.68114583333333334</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>0.68115740740740738</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>0.68116898148148153</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>0.68116898148148153</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>0.68118055555555557</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>0.68119212962962961</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>0.68119212962962961</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>0.68120370370370376</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>0.68121527777777779</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>0.68121527777777779</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>0.68122685185185183</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>0.68123842592592587</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>0.68123842592592587</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>0.68125000000000002</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>0.68126157407407406</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>0.68126157407407406</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>0.6812731481481481</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>0.68128472222222225</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>0.68128472222222225</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>0.68129629629629629</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>0.68130787037037033</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>0.68130787037037033</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>0.68131944444444448</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>0.68133101851851852</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>0.68133101851851852</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>0.68134259259259256</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>0.68135416666666671</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>0.68135416666666671</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>0.68136574074074074</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>0.68137731481481478</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>0.68137731481481478</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>0.68138888888888893</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>0.68140046296296297</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>0.68140046296296297</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>0.68141203703703701</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>0.68142361111111116</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>0.6814351851851852</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>0.6814351851851852</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>0.68144675925925924</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>0.68145833333333339</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>0.68146990740740743</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>0.68146990740740743</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>0.68148148148148147</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>0.6814930555555555</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>0.6814930555555555</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>0.68150462962962965</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>0.68151620370370369</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>0.68151620370370369</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>0.68152777777777773</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>0.68153935185185188</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>0.68153935185185188</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>0.68155092592592592</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>0.68156249999999996</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>0.68156249999999996</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>0.68157407407407411</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>0.68158564814814815</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>0.68159722222222219</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>0.68159722222222219</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>0.68160879629629634</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>0.68162037037037038</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>0.68162037037037038</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>0.68163194444444442</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>0.68164351851851857</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>0.68164351851851857</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>0.6816550925925926</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>0.68166666666666664</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>0.68166666666666664</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>0.68167824074074079</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>0.68168981481481483</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>0.68168981481481483</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>0.68170138888888887</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>0.68171296296296291</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>0.68171296296296291</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>0.68172453703703706</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>0.68172453703703706</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>0.6817361111111111</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>0.68174768518518514</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>0.68174768518518514</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>0.68175925925925929</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>0.68177083333333333</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>0.68177083333333333</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>0.68178240740740736</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>0.68179398148148151</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>0.68179398148148151</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>0.68180555555555555</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>0.68181712962962959</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>0.68181712962962959</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>0.68182870370370374</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>0.68184027777777778</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>0.68184027777777778</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>0.68185185185185182</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>0.68186342592592597</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>0.68186342592592597</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>0.68187500000000001</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>0.68188657407407405</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>0.68188657407407405</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>0.6818981481481482</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>0.68190972222222224</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>0.68190972222222224</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>0.68192129629629628</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>0.68192129629629628</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>0.68193287037037043</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>0.68194444444444446</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>0.68194444444444446</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>0.6819560185185185</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>0.6819560185185185</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>0.68196759259259254</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>0.68197916666666669</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>0.68197916666666669</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>0.68199074074074073</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>0.68200231481481477</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>0.68200231481481477</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>0.68201388888888892</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>0.68202546296296296</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>0.68202546296296296</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>0.682037037037037</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>0.682037037037037</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>0.68204861111111115</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>0.68206018518518519</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>0.68206018518518519</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>0.68207175925925922</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>0.68208333333333337</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>0.68209490740740741</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>0.68209490740740741</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>0.68210648148148145</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>0.6821180555555556</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>0.6821180555555556</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>0.68212962962962964</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>0.68214120370370368</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>0.68214120370370368</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>0.68215277777777783</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>0.68216435185185187</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>0.68216435185185187</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>0.68217592592592591</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>0.68218749999999995</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>0.68218749999999995</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>0.6821990740740741</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>0.68221064814814814</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>0.68222222222222217</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>0.68222222222222217</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>0.68223379629629632</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>0.68223379629629632</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>0.68224537037037036</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>0.6822569444444444</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>0.6822569444444444</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>0.68226851851851855</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>0.68228009259259259</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>0.68229166666666663</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>0.68229166666666663</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>0.68230324074074078</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>0.68231481481481482</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>0.68232638888888886</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>0.68232638888888886</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>0.68233796296296301</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>0.68234953703703705</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>0.68234953703703705</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>0.68236111111111108</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>0.68237268518518523</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>0.68237268518518523</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>0.68238425925925927</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>0.68239583333333331</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>0.68239583333333331</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>0.68240740740740746</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>0.6824189814814815</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>0.6824189814814815</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>0.68243055555555554</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>0.68244212962962958</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>0.68245370370370373</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>0.68245370370370373</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>0.68246527777777777</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>0.68247685185185181</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>0.68247685185185181</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>0.68248842592592596</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>0.6825</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>0.6825</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>0.68251157407407403</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>0.68251157407407403</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>0.68252314814814818</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>0.68253472222222222</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>0.68254629629629626</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>0.68254629629629626</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>0.68255787037037041</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>0.68256944444444445</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>0.68258101851851849</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>0.68258101851851849</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>0.68259259259259264</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>0.68260416666666668</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>0.68260416666666668</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>0.68261574074074072</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>0.68262731481481487</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>0.68262731481481487</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>0.68263888888888891</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>0.68265046296296295</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>0.68266203703703698</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>0.68266203703703698</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>0.68267361111111113</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>0.68268518518518517</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>0.68268518518518517</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>0.68269675925925921</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>0.68270833333333336</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>0.68270833333333336</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>0.6827199074074074</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>0.68273148148148144</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>0.68273148148148144</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>0.68274305555555559</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>0.68275462962962963</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>0.68275462962962963</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>0.68276620370370367</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>0.68277777777777782</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>0.68277777777777782</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>0.68278935185185186</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>0.68280092592592589</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>0.68280092592592589</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>0.68281250000000004</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>0.68282407407407408</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>0.68282407407407408</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>0.68283564814814812</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>0.68284722222222227</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>0.68284722222222227</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>0.68285879629629631</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>0.68287037037037035</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>0.68287037037037035</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>0.6828819444444445</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>0.68289351851851854</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>0.68290509259259258</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>0.68290509259259258</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>0.68291666666666662</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>0.68292824074074077</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>0.68292824074074077</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>0.68293981481481481</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>0.68295138888888884</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>0.68295138888888884</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>0.68296296296296299</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>0.68296296296296299</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>0.68297453703703703</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>0.68298611111111107</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>0.68299768518518522</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>0.68299768518518522</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>0.68300925925925926</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>0.6830208333333333</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>0.6830208333333333</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>0.68303240740740745</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>0.68304398148148149</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>0.68304398148148149</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>0.68305555555555553</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>0.68306712962962968</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>0.68306712962962968</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>0.68307870370370372</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>0.68309027777777775</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>0.68309027777777775</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>0.6831018518518519</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>0.68311342592592594</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>0.68311342592592594</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>0.68312499999999998</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>0.68312499999999998</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>0.68313657407407402</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>0.68314814814814817</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>0.68314814814814817</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>0.68315972222222221</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>0.68317129629629625</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>0.6831828703703704</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>0.6831828703703704</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>0.68319444444444444</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>0.68320601851851848</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>0.68320601851851848</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>0.68321759259259263</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>0.68322916666666667</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>0.68322916666666667</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>0.6832407407407407</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>0.68325231481481485</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>0.68325231481481485</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>0.68326388888888889</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>0.68327546296296293</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>0.68327546296296293</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>0.68328703703703708</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>0.68329861111111112</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>0.68329861111111112</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>0.68331018518518516</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>0.68332175925925931</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>0.68332175925925931</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>0.68333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>0.68334490740740739</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>0.68334490740740739</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>0.68335648148148154</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>0.68335648148148154</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>0.68336805555555558</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>0.68336805555555558</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>0.68337962962962961</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>0.68339120370370365</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>0.68339120370370365</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>0.6834027777777778</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>0.68341435185185184</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>0.68341435185185184</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>0.68342592592592588</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>0.68343750000000003</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>0.68343750000000003</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>0.68344907407407407</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>0.68346064814814811</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>0.68347222222222226</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>0.68347222222222226</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>0.6834837962962963</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>0.6834837962962963</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>0.68349537037037034</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>0.68350694444444449</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>0.68350694444444449</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>0.68351851851851853</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>0.68353009259259256</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>0.68353009259259256</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>0.68354166666666671</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>0.68355324074074075</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>0.68355324074074075</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>0.68356481481481479</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>0.68356481481481479</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>0.68357638888888894</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>0.68358796296296298</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>0.68358796296296298</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>0.68359953703703702</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>0.68359953703703702</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>0.68361111111111106</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>0.68362268518518521</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>0.68362268518518521</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>0.68363425925925925</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>0.68364583333333329</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>0.68364583333333329</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>0.68365740740740744</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>0.68366898148148147</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>0.68366898148148147</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>0.68368055555555551</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>0.68369212962962966</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>0.68369212962962966</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>0.6837037037037037</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>0.68371527777777774</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>0.68372685185185189</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>0.68372685185185189</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>0.68373842592592593</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>0.68374999999999997</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>0.68374999999999997</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>0.68376157407407412</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>0.68377314814814816</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>0.68377314814814816</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>0.6837847222222222</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>0.68379629629629635</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>0.68380787037037039</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>0.68380787037037039</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>0.68381944444444442</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>0.68383101851851846</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>0.68383101851851846</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>0.68384259259259261</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>0.68385416666666665</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>0.68385416666666665</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>0.68386574074074069</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>0.68387731481481484</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>0.68387731481481484</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>0.68388888888888888</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>0.68390046296296292</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>0.68391203703703707</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>0.68391203703703707</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>0.68392361111111111</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>0.68393518518518515</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>0.68393518518518515</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>0.6839467592592593</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>0.68395833333333333</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>0.68395833333333333</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>0.68396990740740737</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>0.68398148148148152</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>0.68399305555555556</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>0.68399305555555556</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>0.6840046296296296</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>0.68401620370370375</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>0.68402777777777779</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$899</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="898"/>
+                <c:pt idx="0">
+                  <c:v>2.6949999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.649</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.6230000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5950000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5710000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5459999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5219999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.4980000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4860000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.431</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.399</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.371</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3039999999999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.254</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.165</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.0750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.0470000000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.0209999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.9970000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.976</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.96</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.94</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.913</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.893</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.8680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.847</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.823</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.804</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7929999999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.7789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.7629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.7509999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.742</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.734</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.722</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.7150000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.7090000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.706</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.7010000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.702</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.704</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.7090000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.7150000000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.7250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.7390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.7549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.7749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.796</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.8140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.8380000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.8660000000000001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.893</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.9179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.9470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.978</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2.0049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2.0350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2.0609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2.09</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2.113</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2.137</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2.157</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2.177</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2.1960000000000002</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2.2130000000000001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2.2269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2.2389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2.2490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2.2559999999999998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2.2599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2.262</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2.2610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2.2589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2.2519999999999998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2.2429999999999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2.21</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2.1909999999999998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2.17</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2.145</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2.1190000000000002</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2.0880000000000001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2.0579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2.0249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1.9910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1.9550000000000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.917</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1.8779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1.839</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1.7989999999999999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1.7609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1.72</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1.681</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1.641</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1.603</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1.5649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.5249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.4890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.4550000000000001</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.369</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.335</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.3009999999999999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.2649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.2290000000000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.194</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.1619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.0680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.0349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.002</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.93300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.86699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.83799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.81200000000000006</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.79200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.77100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.751</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.73099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.71799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.70399999999999996</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.68600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.68500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.69199999999999995</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.70599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.72399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.751</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.77900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.81200000000000006</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.85199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.95199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.012</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.0820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.161</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.2569999999999999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.349</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.4450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.5489999999999999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.66</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.7769999999999999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.893</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>2.008</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>2.1240000000000001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>2.2410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>2.3650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>2.4729999999999999</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>2.59</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>2.7519999999999998</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>2.851</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>2.9460000000000002</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.0409999999999999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.1190000000000002</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.1930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3.2589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3.3149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3.359</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3.39</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3.411</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.42</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.4180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.41</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.3849999999999998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.35</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.3029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3.2549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.2120000000000002</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.1440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3.0649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>2.9209999999999998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>2.8239999999999998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>2.7240000000000002</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>2.6190000000000002</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>2.52</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>2.4209999999999998</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>2.3290000000000002</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>2.2370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>2.149</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>2.0619999999999998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1.9890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1.921</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1.861</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1.81</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1.776</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1.758</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1.7470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1.748</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1.76</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1.7869999999999999</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1.827</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1.8859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.9450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>2.0329999999999999</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>2.1320000000000001</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>2.234</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>2.3410000000000002</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>2.3820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>2.484</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2.5859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>2.68</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>2.7669999999999999</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>2.847</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>2.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>2.9750000000000001</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3.0209999999999999</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3.0529999999999999</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3.0710000000000002</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3.085</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3.0750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3.0489999999999999</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3.03</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2.9460000000000002</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>2.8849999999999998</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>2.835</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>2.7629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>2.6859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>2.6040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.5179999999999998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.4289999999999998</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>2.34</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>2.2519999999999998</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.1619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2.0830000000000002</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1.9910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.905</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1.8160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1.728</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1.6419999999999999</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1.5640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1.4870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1.413</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1.341</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>1.2769999999999999</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>1.2130000000000001</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1.153</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1.0960000000000001</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1.0069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.88100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.85599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.83799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.82499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.81699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.81100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.81100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.81699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.82399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.83699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.85499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.876</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.90100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.96499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1.0029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>1.046</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>1.0920000000000001</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>1.1439999999999999</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>1.323</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>1.3919999999999999</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>1.4650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>1.544</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1.627</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>1.718</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>1.8149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>1.917</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>2.0219999999999998</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>2.1349999999999998</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>2.2519999999999998</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>2.3740000000000001</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>2.496</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>2.6219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>2.88</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>3.0059999999999998</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>3.129</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>3.2480000000000002</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>3.3650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>3.47</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>3.57</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>3.6629999999999998</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>3.7490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>3.81</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>3.863</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>3.9009999999999998</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>3.915</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>3.9239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>3.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>3.895</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>3.847</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>3.798</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3.726</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>3.665</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>3.5819999999999999</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>3.4929999999999999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>3.399</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>3.282</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>3.1760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>3.0659999999999998</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>2.9569999999999999</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>2.847</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>2.7410000000000001</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>2.6259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>2.5259999999999998</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>2.4209999999999998</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>2.3199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>2.2349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>2.1539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>2.0830000000000002</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>2.0179999999999998</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1.96</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>1.907</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>1.8620000000000001</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.8240000000000001</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>1.7929999999999999</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>1.7689999999999999</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>1.7529999999999999</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>1.7450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>1.7430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>1.7490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>1.762</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1.7829999999999999</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1.8089999999999999</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1.8420000000000001</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1.881</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.9259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1.9770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>2.0299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>2.089</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>2.1539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>2.2189999999999999</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>2.2879999999999998</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>2.3610000000000002</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>2.431</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>2.4980000000000002</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>2.5619999999999998</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>2.6280000000000001</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>2.6930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>2.758</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>2.81</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>2.871</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>2.923</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>2.9849999999999999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3.3130000000000002</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3.3730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3.4260000000000002</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3.4550000000000001</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3.4969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3.5350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3.5859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3.6150000000000002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3.641</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3.6619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3.6920000000000002</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>3.7029999999999998</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>3.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3.7170000000000001</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3.7330000000000001</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3.7549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>3.782</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3.8130000000000002</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3.8660000000000001</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>3.9140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>3.9660000000000002</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4.0129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4.0670000000000002</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4.1189999999999998</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4.1760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4.234</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4.2839999999999998</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4.335</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4.3769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4.4109999999999996</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4.4489999999999998</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4.4770000000000003</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4.5019999999999998</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4.5199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4.516</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4.4870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4.3719999999999999</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4.2770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4.1760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4.0640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>3.9420000000000002</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>3.8109999999999999</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>3.6720000000000002</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>3.53</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3.4020000000000001</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>3.2650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>3.1320000000000001</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>3.008</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>2.8929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>2.7890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>2.681</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>2.5819999999999999</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>2.4940000000000002</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>2.42</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>2.3519999999999999</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>2.2949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>2.2480000000000002</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>2.214</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>2.1890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>2.1709999999999998</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>2.1619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>2.1579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>2.1619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>2.169</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>2.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>2.2040000000000002</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>2.23</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>2.2599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>2.2989999999999999</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>2.343</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>2.3940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>2.4489999999999998</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>2.5089999999999999</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>2.577</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>2.65</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>2.73</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>2.8149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>2.9049999999999998</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>3.0049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>3.2450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3.37</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>3.5030000000000001</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>3.6480000000000001</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>3.7949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>3.944</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>3.9239999999999999</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4.0670000000000002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4.2160000000000002</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4.54</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4.8029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4.9160000000000004</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5.0190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>5.1100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5.1639999999999997</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>5.2169999999999996</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>5.2350000000000003</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>5.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>5.194</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>5.1189999999999998</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5.0199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4.8929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4.7549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4.6630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4.5129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4.3230000000000004</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4.1340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>3.94</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>3.7389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>3.3969999999999998</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>3.1909999999999998</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>2.992</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>2.8210000000000002</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>2.669</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>2.5470000000000002</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>2.4409999999999998</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>2.3479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>2.2599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>2.1920000000000002</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>2.1419999999999999</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>2.1139999999999999</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>2.1070000000000002</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>2.1160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>2.1379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>2.1930000000000001</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>2.2629999999999999</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>2.3370000000000002</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>2.427</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>2.52</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>2.633</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>2.7309999999999999</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>2.835</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>2.9430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>3.052</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>3.1579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>3.2589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>3.355</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>3.4350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>3.508</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>3.5659999999999998</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>3.605</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>3.6269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>3.633</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>3.6219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>3.5579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>3.5030000000000001</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>3.431</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>3.3410000000000002</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>3.2440000000000002</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>3.1320000000000001</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>2.8679999999999999</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>2.7349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>2.5950000000000002</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>2.4540000000000002</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>2.3170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>2.1850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>2.0569999999999999</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>1.9350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>1.8220000000000001</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>1.718</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>1.6120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.526</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>1.4570000000000001</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>1.3859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>1.325</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>1.2230000000000001</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>1.1850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>1.1519999999999999</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>1.131</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.115</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.099</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.087</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>1.0880000000000001</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>1.0980000000000001</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>1.1080000000000001</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.119</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>1.1399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>1.147</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>1.149</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>1.1479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>1.1459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>1.135</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>1.119</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>1.097</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>1.0720000000000001</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>1.046</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>1.018</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>0.97399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>0.94099999999999995</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>0.90700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>0.88500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>0.84899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>0.80900000000000005</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>0.77400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>0.73499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>0.70399999999999996</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>0.66200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>0.64100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>0.623</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>0.61199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>0.60799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>0.60899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>0.61499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>0.65300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>0.69099999999999995</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>0.73099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>0.79100000000000004</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>0.86699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>0.95899999999999996</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>1.0609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>1.181</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>1.3180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>1.4850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>1.657</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>1.8440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>2.0529999999999999</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>2.2850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>2.5369999999999999</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>2.7869999999999999</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>3.0550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>3.3319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>3.6240000000000001</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>3.9129999999999998</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>4.1980000000000004</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>4.4809999999999999</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>4.7560000000000002</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>5.0170000000000003</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>5.2519999999999998</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>5.468</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>5.6660000000000004</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>5.8330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>5.7690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>5.8849999999999998</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>5.9969999999999999</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>6.0839999999999996</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>6.1340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>6.1760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>6.181</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>6.1829999999999998</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>6.141</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>6.0789999999999997</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>6.02</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>5.9189999999999996</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>5.8019999999999996</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>5.6559999999999997</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>5.5410000000000004</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>5.3769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>5.2279999999999998</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>5.0810000000000004</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>4.9390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>4.7949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>4.67</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>4.54</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>4.4290000000000003</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>4.3259999999999996</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>4.2329999999999997</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>4.1580000000000004</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>4.0960000000000001</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>4.09</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>4.0590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>4.0469999999999997</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>4.056</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>4.0860000000000003</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>4.133</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>4.2160000000000002</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>4.306</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>4.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>4.5350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>4.694</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>4.8680000000000003</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>5.0910000000000002</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>5.3209999999999997</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>5.5960000000000001</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>5.8639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>6.1840000000000002</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>6.4909999999999997</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>6.84</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>7.2030000000000003</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>7.6029999999999998</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>7.9710000000000001</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>8.3559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>8.7409999999999997</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>9.0960000000000001</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>9.4239999999999995</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>9.7530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>10.050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>10.292</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>10.532</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>10.746</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>10.898999999999999</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>11.002000000000001</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>11.077999999999999</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>11.11</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>11.101000000000001</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>11.061</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>11.032999999999999</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>10.972</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>10.907999999999999</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>10.840999999999999</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>10.772</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>10.673999999999999</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>10.548999999999999</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>10.4</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>10.401</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>10.254</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>10.103999999999999</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>9.7850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>9.6669999999999998</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>9.5329999999999995</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>9.3930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>9.2330000000000005</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>9.0579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>8.8930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>8.7140000000000004</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>8.5310000000000006</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>8.3390000000000004</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>8.1620000000000008</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>7.9870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>7.8159999999999998</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>7.6479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>7.48</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>7.3049999999999997</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>7.1289999999999996</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>6.94</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>6.6040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>6.4189999999999996</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>6.2329999999999997</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>6.048</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>5.8680000000000003</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>5.702</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>5.5339999999999998</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>5.3769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>5.2169999999999996</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>5.0609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>4.9210000000000003</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>4.7809999999999997</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>4.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>4.5460000000000003</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>4.46</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>4.3840000000000003</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>4.3230000000000004</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>4.2859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>4.2590000000000003</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>4.2619999999999996</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>4.3330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>4.3890000000000002</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>4.4619999999999997</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>4.5540000000000003</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>4.665</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>4.8010000000000002</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>5.101</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>5.3209999999999997</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>5.5640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>5.8570000000000002</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>6.1859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>6.5369999999999999</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>6.9210000000000003</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>7.3380000000000001</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>7.8070000000000004</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>8.3019999999999996</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>8.81</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>9.3699999999999992</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>9.9770000000000003</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>10.646000000000001</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>11.331</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>12.086</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>12.872</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>13.624000000000001</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>14.317</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>14.977</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>15.54</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>15.987</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>16.312999999999999</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>16.524999999999999</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>16.61</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>16.558</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>16.376000000000001</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>16.128</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>15.669</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>15.172000000000001</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>14.548999999999999</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>13.776999999999999</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>13.047000000000001</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>12.243</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>11.538</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>10.824999999999999</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>10.127000000000001</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>9.4580000000000002</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>8.8379999999999992</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>8.2379999999999995</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>7.6829999999999998</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>7.1340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>6.6219999999999999</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>6.17</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>5.742</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>5.3680000000000003</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>5.0490000000000004</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>4.78</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>4.5570000000000004</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>4.3860000000000001</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>4.2590000000000003</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>4.1689999999999996</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>4.125</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>4.101</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>4.0990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>4.1040000000000001</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>4.1360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>4.1779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>4.242</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>4.3070000000000004</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>4.3369999999999997</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>4.4089999999999998</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>4.4930000000000003</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>4.5819999999999999</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>4.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>4.7670000000000003</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>4.8550000000000004</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>4.9420000000000002</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>5.0259999999999998</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>5.1070000000000002</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>5.1929999999999996</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>5.2809999999999997</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>5.3710000000000004</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>5.468</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>5.569</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>5.6719999999999997</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>5.7690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>5.86</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>5.9470000000000001</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>6.0229999999999997</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>6.0890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>6.1459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>6.1950000000000003</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>6.234</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>6.226</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>6.2560000000000002</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>6.2750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>6.2839999999999998</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>6.2859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>6.28</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>6.2679999999999998</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>6.2430000000000003</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>6.2080000000000002</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>6.1870000000000003</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>6.1349999999999998</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>6.0730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>6.0049999999999999</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>5.9349999999999996</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>5.8479999999999999</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>5.7530000000000001</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>5.6539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>5.55</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>5.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>5.3360000000000003</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>5.2169999999999996</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>5.1310000000000002</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>5.03</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>4.9379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>4.8570000000000002</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>4.7789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>4.7080000000000002</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>4.6630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>4.609</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>4.5659999999999998</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>4.532</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>4.5060000000000002</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>4.4930000000000003</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>4.5010000000000003</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>4.5209999999999999</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>4.569</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>4.5759999999999996</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>4.6589999999999998</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>4.76</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>4.875</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>4.9989999999999997</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>5.1429999999999998</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>5.3040000000000003</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>5.4880000000000004</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>5.6959999999999997</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>5.9260000000000002</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>6.2069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>6.4880000000000004</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>6.7910000000000004</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>7.117</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>7.4640000000000004</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>7.8140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>8.1470000000000002</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>8.5299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>8.923</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>9.3179999999999996</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>9.7129999999999992</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>10.06</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>10.375999999999999</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>10.663</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>10.91</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>11.093</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>11.249000000000001</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>11.365</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>11.427</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>11.461</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>11.539</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>11.452</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>11.337</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>11.246</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>11.087999999999999</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>10.938000000000001</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>10.747</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>10.545999999999999</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>10.276999999999999</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>9.9979999999999993</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>9.7210000000000001</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>9.3819999999999997</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>9.02</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>8.6470000000000002</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>8.2989999999999995</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>7.9050000000000002</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>7.5359999999999996</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>7.1669999999999998</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>6.7949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>6.4219999999999997</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>6.0609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>5.72</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>5.3780000000000001</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>5.0730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>4.7610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>4.476</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>4.21</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>3.802</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-250D-4201-A194-344C70C92763}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="338678912"/>
+        <c:axId val="338679392"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="338678912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="h:mm:ss" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="338679392"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="338679392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>LFHF values</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="338678912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>887</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>902</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D21E296-E10E-E574-BA2A-E93556095900}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>899</xdr:row>
+      <xdr:rowOff>142435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>205153</xdr:colOff>
+      <xdr:row>902</xdr:row>
+      <xdr:rowOff>64477</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4A42CFA-1A40-1104-3BFA-CA0186E610E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5326380" y="163497650"/>
+          <a:ext cx="4022773" cy="467165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" kern="1200"/>
+            <a:t>0                                                          </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" kern="1200" baseline="0"/>
+            <a:t>                          5                                                                                 10</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="900" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114985</xdr:colOff>
+      <xdr:row>901</xdr:row>
+      <xdr:rowOff>13809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>453601</xdr:colOff>
+      <xdr:row>902</xdr:row>
+      <xdr:rowOff>56144</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47088AC0-415C-B50F-207E-1A24F6F6B95F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6820585" y="163732440"/>
+          <a:ext cx="948216" cy="224042"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" kern="1200"/>
+            <a:t>Time (minutes)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>568568</xdr:colOff>
+      <xdr:row>890</xdr:row>
+      <xdr:rowOff>52753</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>96977</xdr:colOff>
+      <xdr:row>899</xdr:row>
+      <xdr:rowOff>105507</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2926FA9D-50AF-4BFA-82CC-201F6559D515}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7274168" y="161772599"/>
+          <a:ext cx="1966809" cy="1688123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="84E291">
+            <a:alpha val="16863"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11528,5 +18248,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>